--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260917.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260917.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.47%</t>
+          <t>10.68%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>4,750,000</t>
+          <t>5,186,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>8.67%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5,186,000</t>
+          <t>4,750,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.71%</t>
+          <t>8.28%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>7.09%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.00%</t>
+          <t>7.04%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.28%</t>
+          <t>5.20%</t>
         </is>
       </c>
     </row>
@@ -743,56 +743,56 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>6,490,561</t>
+          <t>6,332,561</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.21%</t>
+          <t>5.02%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>24,987,000</t>
+          <t>2,512,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.96%</t>
+          <t>5.00%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>2,512,000</t>
+          <t>24,987,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.91%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.88%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.53%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.41%</t>
+          <t>4.32%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>9,426,000</t>
+          <t>16,811,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.83%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>16,811,000</t>
+          <t>9,426,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.73%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.20%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
@@ -1056,68 +1056,68 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>446,000</t>
+          <t>6,628,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>1,516,000</t>
+          <t>446,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,712,000</t>
+          <t>1,516,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,22 +1129,22 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>5,028,000</t>
+          <t>2,712,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>4,559,671,641</t>
+          <t>6,705,165,317</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,860,923,397</t>
+          <t>1,915,107,597</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-46,750,072</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>1,411,097,300</t>
+          <t>1,670,236,766</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
